--- a/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
@@ -529,7 +529,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -538,13 +538,13 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>91.18000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -555,10 +555,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -567,7 +567,7 @@
         <v>36</v>
       </c>
       <c r="G5">
-        <v>92.31</v>
+        <v>90</v>
       </c>
       <c r="H5">
         <v>9.5</v>
@@ -718,13 +718,13 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -741,10 +741,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5">
         <v>39</v>
@@ -901,7 +901,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -910,13 +910,13 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>91.18000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -927,10 +927,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -939,7 +939,7 @@
         <v>36</v>
       </c>
       <c r="G5">
-        <v>92.31</v>
+        <v>90</v>
       </c>
       <c r="H5">
         <v>9.5</v>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -80,6 +80,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>JOEL MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -529,7 +538,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -538,13 +547,13 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>91.43000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -718,13 +727,13 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -901,7 +910,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -910,13 +919,13 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>91.43000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1004,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1034,6 +1043,29 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920024</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
@@ -684,16 +684,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>85.19</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -707,16 +710,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H3">
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -730,16 +736,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>91.18000000000001</v>
+      </c>
+      <c r="H4">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -753,16 +762,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H5">
+        <v>9.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -776,16 +788,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>94.87</v>
+      </c>
+      <c r="H6">
+        <v>9.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -799,16 +814,19 @@
         <v>30</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>30</v>
       </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -864,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>77.78</v>
+        <v>85.19</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -890,16 +908,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>91.67</v>
+        <v>87.5</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -925,7 +943,7 @@
         <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -951,7 +969,7 @@
         <v>90</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -968,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>92.31</v>
+        <v>94.87</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -994,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>96.67</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
@@ -567,10 +567,10 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>36</v>
@@ -579,7 +579,7 @@
         <v>90</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -762,10 +762,10 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>36</v>
@@ -774,7 +774,7 @@
         <v>90</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -957,10 +957,10 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>36</v>
@@ -969,7 +969,7 @@
         <v>90</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,15 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>JOEL MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -882,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>85.19</v>
+        <v>77.78</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -908,16 +899,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -943,7 +934,7 @@
         <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -960,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -995,7 +986,7 @@
         <v>94.87</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1012,16 +1003,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1061,29 +1052,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920024</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
@@ -882,7 +882,7 @@
         <v>77.78</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -908,7 +908,7 @@
         <v>91.67</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -934,7 +934,7 @@
         <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -960,7 +960,7 @@
         <v>95</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -986,7 +986,7 @@
         <v>94.87</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1012,7 +1012,7 @@
         <v>96.67</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20231.xlsx
@@ -882,7 +882,7 @@
         <v>77.78</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -908,7 +908,7 @@
         <v>91.67</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -934,7 +934,7 @@
         <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -960,7 +960,7 @@
         <v>95</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -986,7 +986,7 @@
         <v>94.87</v>
       </c>
       <c r="H6">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1012,7 +1012,7 @@
         <v>96.67</v>
       </c>
       <c r="H7">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
